--- a/data/2023/counties_2023.xlsx
+++ b/data/2023/counties_2023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djei.cloud.gov.ie/apps/eDocs/S/ENT218/Files/ENT218-001-2023/Web Stats 2023/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{51A7AF05-0907-419F-AC8B-D079A61B540A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E26AC47-9DC1-419F-ACCF-6768D0F66AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{1D09E6E9-FE6D-4367-975D-34461A458503}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1D09E6E9-FE6D-4367-975D-34461A458503}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,10 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
-  <si>
-    <t>2023</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Issued</t>
   </si>
@@ -46,12 +43,6 @@
     <t>Refused</t>
   </si>
   <si>
-    <t>Withdrawn</t>
-  </si>
-  <si>
-    <t>Grand Total</t>
-  </si>
-  <si>
     <t>Carlow</t>
   </si>
   <si>
@@ -134,6 +125,9 @@
   </si>
   <si>
     <t xml:space="preserve">No County Entered </t>
+  </si>
+  <si>
+    <t>County</t>
   </si>
 </sst>
 </file>
@@ -141,7 +135,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
@@ -221,9 +215,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -235,16 +229,6 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -265,9 +249,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -305,7 +289,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -411,7 +395,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -553,7 +537,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -561,447 +545,386 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{354CB108-41A1-4F8F-9FD4-E571366B611E}">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
     <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="4"/>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2" s="7" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="3">
+        <v>75</v>
+      </c>
+      <c r="C2" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="B3" s="3">
+        <v>161</v>
+      </c>
+      <c r="C3" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="B4" s="3">
+        <v>312</v>
+      </c>
+      <c r="C4" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="9">
-        <v>30981</v>
-      </c>
-      <c r="C3" s="9">
-        <v>1575</v>
-      </c>
-      <c r="D3" s="9">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="3">
-        <v>75</v>
-      </c>
-      <c r="C4" s="3">
+      <c r="B5" s="3">
+        <v>496</v>
+      </c>
+      <c r="C5" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3">
+        <v>2613</v>
+      </c>
+      <c r="C6" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3">
+        <v>387</v>
+      </c>
+      <c r="C8" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3">
+        <v>15401</v>
+      </c>
+      <c r="C9" s="3">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="3">
+      <c r="B10" s="3">
+        <v>1387</v>
+      </c>
+      <c r="C10" s="3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3">
+        <v>384</v>
+      </c>
+      <c r="C11" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1734</v>
+      </c>
+      <c r="C12" s="3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3">
+        <v>491</v>
+      </c>
+      <c r="C13" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3">
+        <v>213</v>
+      </c>
+      <c r="C14" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3">
+        <v>54</v>
+      </c>
+      <c r="C15" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3">
+        <v>1600</v>
+      </c>
+      <c r="C16" s="3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="3">
-        <v>161</v>
-      </c>
-      <c r="C5" s="3">
-        <v>7</v>
-      </c>
-      <c r="D5" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="3">
-        <v>312</v>
-      </c>
-      <c r="C6" s="3">
+      <c r="B17" s="3">
+        <v>120</v>
+      </c>
+      <c r="C17" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3">
+        <v>649</v>
+      </c>
+      <c r="C18" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="3">
-        <v>496</v>
-      </c>
-      <c r="C7" s="3">
-        <v>30</v>
-      </c>
-      <c r="D7" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="B19" s="3">
+        <v>378</v>
+      </c>
+      <c r="C19" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3">
+        <v>1137</v>
+      </c>
+      <c r="C20" s="3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3">
+        <v>240</v>
+      </c>
+      <c r="C21" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3">
+        <v>328</v>
+      </c>
+      <c r="C22" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3">
+        <v>138</v>
+      </c>
+      <c r="C23" s="3">
         <v>8</v>
       </c>
-      <c r="B8" s="3">
-        <v>2613</v>
-      </c>
-      <c r="C8" s="3">
-        <v>123</v>
-      </c>
-      <c r="D8" s="3">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="3">
-        <v>1</v>
-      </c>
-      <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="3">
-        <v>387</v>
-      </c>
-      <c r="C10" s="3">
-        <v>19</v>
-      </c>
-      <c r="D10" s="3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="3">
-        <v>15401</v>
-      </c>
-      <c r="C11" s="3">
-        <v>752</v>
-      </c>
-      <c r="D11" s="3">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="3">
-        <v>1387</v>
-      </c>
-      <c r="C12" s="3">
-        <v>85</v>
-      </c>
-      <c r="D12" s="3">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="3">
-        <v>384</v>
-      </c>
-      <c r="C13" s="3">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3">
+        <v>220</v>
+      </c>
+      <c r="C24" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3">
+        <v>531</v>
+      </c>
+      <c r="C25" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3">
+        <v>660</v>
+      </c>
+      <c r="C26" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="3">
-        <v>1734</v>
-      </c>
-      <c r="C14" s="3">
-        <v>53</v>
-      </c>
-      <c r="D14" s="3">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="3">
-        <v>491</v>
-      </c>
-      <c r="C15" s="3">
-        <v>24</v>
-      </c>
-      <c r="D15" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="3">
-        <v>213</v>
-      </c>
-      <c r="C16" s="3">
-        <v>14</v>
-      </c>
-      <c r="D16" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="3">
-        <v>54</v>
-      </c>
-      <c r="C17" s="3">
-        <v>5</v>
-      </c>
-      <c r="D17" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="3">
-        <v>1600</v>
-      </c>
-      <c r="C18" s="3">
-        <v>84</v>
-      </c>
-      <c r="D18" s="3">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="3">
-        <v>120</v>
-      </c>
-      <c r="C19" s="3">
-        <v>13</v>
-      </c>
-      <c r="D19" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="3">
-        <v>649</v>
-      </c>
-      <c r="C20" s="3">
-        <v>20</v>
-      </c>
-      <c r="D20" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="B27" s="3">
+        <v>391</v>
+      </c>
+      <c r="C27" s="3">
         <v>21</v>
       </c>
-      <c r="B21" s="3">
-        <v>378</v>
-      </c>
-      <c r="C21" s="3">
-        <v>19</v>
-      </c>
-      <c r="D21" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="3">
-        <v>1137</v>
-      </c>
-      <c r="C22" s="3">
-        <v>53</v>
-      </c>
-      <c r="D22" s="3">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="3">
-        <v>240</v>
-      </c>
-      <c r="C23" s="3">
-        <v>34</v>
-      </c>
-      <c r="D23" s="3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="3">
-        <v>328</v>
-      </c>
-      <c r="C24" s="3">
-        <v>10</v>
-      </c>
-      <c r="D24" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="3">
-        <v>138</v>
-      </c>
-      <c r="C25" s="3">
-        <v>8</v>
-      </c>
-      <c r="D25" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="3">
-        <v>220</v>
-      </c>
-      <c r="C26" s="3">
-        <v>20</v>
-      </c>
-      <c r="D26" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="3">
-        <v>531</v>
-      </c>
-      <c r="C27" s="3">
-        <v>33</v>
-      </c>
-      <c r="D27" s="3">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="B28" s="3">
+        <v>606</v>
+      </c>
+      <c r="C28" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="3">
-        <v>660</v>
-      </c>
-      <c r="C28" s="3">
-        <v>16</v>
-      </c>
-      <c r="D28" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="B29" s="3">
-        <v>391</v>
+        <v>275</v>
       </c>
       <c r="C29" s="3">
-        <v>21</v>
-      </c>
-      <c r="D29" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="3">
-        <v>606</v>
-      </c>
-      <c r="C30" s="3">
-        <v>31</v>
-      </c>
-      <c r="D30" s="3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" s="3">
-        <v>275</v>
-      </c>
-      <c r="C31" s="3">
         <v>47</v>
       </c>
-      <c r="D31" s="3">
-        <v>5</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B1:D1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <m02c691f3efa402dab5cbaa8c240a9e7 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </m02c691f3efa402dab5cbaa8c240a9e7>
+    <TaxCatchAll xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
+      <Value>5</Value>
+      <Value>1</Value>
+    </TaxCatchAll>
+    <eDocs_FileStatus xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">Live</eDocs_FileStatus>
+    <h1f8bb4843d6459a8b809123185593c7 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">218</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">d1f665d0-1ea2-48c4-9fae-9dfb881d0110</TermId>
+        </TermInfo>
+      </Terms>
+    </h1f8bb4843d6459a8b809123185593c7>
+    <fbaa881fc4ae443f9fdafbdd527793df xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </fbaa881fc4ae443f9fdafbdd527793df>
+    <_vti_ItemDeclaredRecord xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd" xsi:nil="true"/>
+    <nb1b8a72855341e18dd75ce464e281f2 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </nb1b8a72855341e18dd75ce464e281f2>
+    <eDocs_eFileName xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd" xsi:nil="true"/>
+    <mbbd3fafa5ab4e5eb8a6a5e099cef439 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Unclassified</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">779752a3-a421-4077-839c-91815f544ae2</TermId>
+        </TermInfo>
+      </Terms>
+    </mbbd3fafa5ab4e5eb8a6a5e099cef439>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="eDocument" ma:contentTypeID="0x0101000BC94875665D404BB1351B53C41FD2C000E5CBA74D75A77049B177D97877D56E03" ma:contentTypeVersion="55" ma:contentTypeDescription="" ma:contentTypeScope="" ma:versionID="849aa1d06b04c28173376e708035b9cb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f94102a1-1d6c-4502-ac27-91905b9321dd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="26a80217159fa0c72fe0406038957729" ns2:_="">
     <xsd:import namespace="f94102a1-1d6c-4502-ac27-91905b9321dd"/>
@@ -1210,55 +1133,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DAC337C-2432-4E02-A712-54EF5FD32DAF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="f94102a1-1d6c-4502-ac27-91905b9321dd"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <m02c691f3efa402dab5cbaa8c240a9e7 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </m02c691f3efa402dab5cbaa8c240a9e7>
-    <TaxCatchAll xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
-      <Value>5</Value>
-      <Value>1</Value>
-    </TaxCatchAll>
-    <eDocs_FileStatus xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">Live</eDocs_FileStatus>
-    <h1f8bb4843d6459a8b809123185593c7 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">218</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">d1f665d0-1ea2-48c4-9fae-9dfb881d0110</TermId>
-        </TermInfo>
-      </Terms>
-    </h1f8bb4843d6459a8b809123185593c7>
-    <fbaa881fc4ae443f9fdafbdd527793df xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </fbaa881fc4ae443f9fdafbdd527793df>
-    <_vti_ItemDeclaredRecord xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd" xsi:nil="true"/>
-    <nb1b8a72855341e18dd75ce464e281f2 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </nb1b8a72855341e18dd75ce464e281f2>
-    <eDocs_eFileName xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd" xsi:nil="true"/>
-    <mbbd3fafa5ab4e5eb8a6a5e099cef439 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Unclassified</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">779752a3-a421-4077-839c-91815f544ae2</TermId>
-        </TermInfo>
-      </Terms>
-    </mbbd3fafa5ab4e5eb8a6a5e099cef439>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5C191D3-3A6D-47EA-99B8-12E929ECC95C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0F6E3A1-5BCC-4C50-A920-A094C0C41581}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1274,28 +1173,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5C191D3-3A6D-47EA-99B8-12E929ECC95C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DAC337C-2432-4E02-A712-54EF5FD32DAF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="f94102a1-1d6c-4502-ac27-91905b9321dd"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>